--- a/cuestionarios/DEBERES 26.xlsx
+++ b/cuestionarios/DEBERES 26.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\comciberdef.gdia01\Videos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ville020\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D7E4A2-452A-48E0-A18D-D4B0795BD6D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="CUESTIONARIO-2026" sheetId="1" r:id="rId1"/>
@@ -6207,7 +6206,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -6563,8 +6562,8 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{F3980104-4ABB-4F82-8F44-DE3D63FC9D67}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
   </cellStyles>
   <dxfs count="24">
     <dxf>
@@ -7116,7 +7115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G575"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12919,6 +12918,9 @@
       </c>
     </row>
     <row r="255" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="6">
+        <v>251</v>
+      </c>
       <c r="B255" s="9" t="s">
         <v>245</v>
       </c>
@@ -12939,6 +12941,9 @@
       </c>
     </row>
     <row r="256" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="6">
+        <v>252</v>
+      </c>
       <c r="B256" s="9" t="s">
         <v>246</v>
       </c>
@@ -12958,7 +12963,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="6">
+        <v>253</v>
+      </c>
       <c r="B257" s="9" t="s">
         <v>247</v>
       </c>
@@ -12978,7 +12986,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="6">
+        <v>254</v>
+      </c>
       <c r="B258" s="9" t="s">
         <v>248</v>
       </c>
@@ -12998,7 +13009,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="6">
+        <v>255</v>
+      </c>
       <c r="B259" s="9" t="s">
         <v>249</v>
       </c>
@@ -13018,7 +13032,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="6">
+        <v>256</v>
+      </c>
       <c r="B260" s="9" t="s">
         <v>250</v>
       </c>
@@ -13038,7 +13055,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="6">
+        <v>257</v>
+      </c>
       <c r="B261" s="9" t="s">
         <v>251</v>
       </c>
@@ -13058,7 +13078,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="6">
+        <v>258</v>
+      </c>
       <c r="B262" s="9" t="s">
         <v>252</v>
       </c>
@@ -13078,7 +13101,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="6">
+        <v>259</v>
+      </c>
       <c r="B263" s="9" t="s">
         <v>253</v>
       </c>
@@ -13098,7 +13124,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="6">
+        <v>260</v>
+      </c>
       <c r="B264" s="9" t="s">
         <v>254</v>
       </c>
@@ -13118,7 +13147,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="6">
+        <v>261</v>
+      </c>
       <c r="B265" s="9" t="s">
         <v>255</v>
       </c>
@@ -13138,7 +13170,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="6">
+        <v>262</v>
+      </c>
       <c r="B266" s="9" t="s">
         <v>256</v>
       </c>
@@ -13158,7 +13193,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="6">
+        <v>263</v>
+      </c>
       <c r="B267" s="14" t="s">
         <v>257</v>
       </c>
@@ -13178,7 +13216,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="6">
+        <v>264</v>
+      </c>
       <c r="B268" s="14" t="s">
         <v>258</v>
       </c>
@@ -13198,7 +13239,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="6">
+        <v>265</v>
+      </c>
       <c r="B269" s="14" t="s">
         <v>259</v>
       </c>
@@ -13218,7 +13262,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="6">
+        <v>266</v>
+      </c>
       <c r="B270" s="14" t="s">
         <v>260</v>
       </c>
@@ -13238,7 +13285,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="6">
+        <v>267</v>
+      </c>
       <c r="B271" s="14" t="s">
         <v>261</v>
       </c>
@@ -13258,7 +13308,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="6">
+        <v>268</v>
+      </c>
       <c r="B272" s="14" t="s">
         <v>262</v>
       </c>
@@ -13278,7 +13331,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="6">
+        <v>269</v>
+      </c>
       <c r="B273" s="14" t="s">
         <v>263</v>
       </c>
@@ -13298,7 +13354,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="274" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="6">
+        <v>270</v>
+      </c>
       <c r="B274" s="14" t="s">
         <v>264</v>
       </c>
@@ -13318,7 +13377,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="6">
+        <v>271</v>
+      </c>
       <c r="B275" s="14" t="s">
         <v>265</v>
       </c>
@@ -13338,7 +13400,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="6">
+        <v>272</v>
+      </c>
       <c r="B276" s="14" t="s">
         <v>266</v>
       </c>
@@ -13358,7 +13423,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="6">
+        <v>273</v>
+      </c>
       <c r="B277" s="14" t="s">
         <v>267</v>
       </c>
@@ -13378,7 +13446,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="6">
+        <v>274</v>
+      </c>
       <c r="B278" s="14" t="s">
         <v>268</v>
       </c>
@@ -13398,7 +13469,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="6">
+        <v>275</v>
+      </c>
       <c r="B279" s="14" t="s">
         <v>269</v>
       </c>
@@ -13418,7 +13492,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="6">
+        <v>276</v>
+      </c>
       <c r="B280" s="14" t="s">
         <v>270</v>
       </c>
@@ -13438,7 +13515,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="6">
+        <v>277</v>
+      </c>
       <c r="B281" s="14" t="s">
         <v>271</v>
       </c>
@@ -13458,7 +13538,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="6">
+        <v>278</v>
+      </c>
       <c r="B282" s="14" t="s">
         <v>272</v>
       </c>
@@ -13478,7 +13561,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="6">
+        <v>279</v>
+      </c>
       <c r="B283" s="14" t="s">
         <v>273</v>
       </c>
@@ -13498,7 +13584,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="6">
+        <v>280</v>
+      </c>
       <c r="B284" s="14" t="s">
         <v>274</v>
       </c>
@@ -13518,7 +13607,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="6">
+        <v>281</v>
+      </c>
       <c r="B285" s="14" t="s">
         <v>275</v>
       </c>
@@ -13538,7 +13630,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="6">
+        <v>282</v>
+      </c>
       <c r="B286" s="14" t="s">
         <v>276</v>
       </c>
@@ -13558,7 +13653,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="6">
+        <v>283</v>
+      </c>
       <c r="B287" s="14" t="s">
         <v>277</v>
       </c>
@@ -13578,7 +13676,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="6">
+        <v>284</v>
+      </c>
       <c r="B288" s="14" t="s">
         <v>278</v>
       </c>
@@ -13598,7 +13699,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="6">
+        <v>285</v>
+      </c>
       <c r="B289" s="14" t="s">
         <v>279</v>
       </c>
@@ -13618,7 +13722,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="6">
+        <v>286</v>
+      </c>
       <c r="B290" s="14" t="s">
         <v>280</v>
       </c>
@@ -13638,7 +13745,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="6">
+        <v>287</v>
+      </c>
       <c r="B291" s="14" t="s">
         <v>281</v>
       </c>
@@ -13658,7 +13768,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="6">
+        <v>288</v>
+      </c>
       <c r="B292" s="14" t="s">
         <v>282</v>
       </c>
@@ -13678,7 +13791,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="6">
+        <v>289</v>
+      </c>
       <c r="B293" s="14" t="s">
         <v>283</v>
       </c>
@@ -13698,7 +13814,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="6">
+        <v>290</v>
+      </c>
       <c r="B294" s="15" t="s">
         <v>284</v>
       </c>
@@ -13718,7 +13837,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="6">
+        <v>291</v>
+      </c>
       <c r="B295" s="15" t="s">
         <v>285</v>
       </c>
@@ -13738,7 +13860,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="6">
+        <v>292</v>
+      </c>
       <c r="B296" s="15" t="s">
         <v>286</v>
       </c>
@@ -13758,7 +13883,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="6">
+        <v>293</v>
+      </c>
       <c r="B297" s="15" t="s">
         <v>287</v>
       </c>
@@ -13778,7 +13906,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="6">
+        <v>294</v>
+      </c>
       <c r="B298" s="15" t="s">
         <v>288</v>
       </c>
@@ -13798,7 +13929,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="6">
+        <v>295</v>
+      </c>
       <c r="B299" s="15" t="s">
         <v>289</v>
       </c>
@@ -13818,7 +13952,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="6">
+        <v>296</v>
+      </c>
       <c r="B300" s="15" t="s">
         <v>290</v>
       </c>
@@ -13838,7 +13975,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="6">
+        <v>297</v>
+      </c>
       <c r="B301" s="15" t="s">
         <v>291</v>
       </c>
@@ -13858,7 +13998,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="6">
+        <v>298</v>
+      </c>
       <c r="B302" s="15" t="s">
         <v>291</v>
       </c>
@@ -13878,7 +14021,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="6">
+        <v>299</v>
+      </c>
       <c r="B303" s="15" t="s">
         <v>291</v>
       </c>
@@ -13898,7 +14044,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="6">
+        <v>300</v>
+      </c>
       <c r="B304" s="15" t="s">
         <v>291</v>
       </c>
@@ -13918,7 +14067,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A305" s="6">
+        <v>301</v>
+      </c>
       <c r="B305" s="15" t="s">
         <v>291</v>
       </c>
@@ -13938,7 +14090,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="6">
+        <v>302</v>
+      </c>
       <c r="B306" s="15" t="s">
         <v>291</v>
       </c>
@@ -13958,7 +14113,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="6">
+        <v>303</v>
+      </c>
       <c r="B307" s="15" t="s">
         <v>291</v>
       </c>
@@ -13978,7 +14136,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="6">
+        <v>304</v>
+      </c>
       <c r="B308" s="15" t="s">
         <v>291</v>
       </c>
@@ -13998,7 +14159,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="6">
+        <v>305</v>
+      </c>
       <c r="B309" s="15" t="s">
         <v>291</v>
       </c>
@@ -14018,7 +14182,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A310" s="6">
+        <v>306</v>
+      </c>
       <c r="B310" s="15" t="s">
         <v>291</v>
       </c>
@@ -14038,7 +14205,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="6">
+        <v>307</v>
+      </c>
       <c r="B311" s="15" t="s">
         <v>291</v>
       </c>
@@ -14058,7 +14228,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A312" s="6">
+        <v>308</v>
+      </c>
       <c r="B312" s="15" t="s">
         <v>291</v>
       </c>
@@ -14078,7 +14251,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="6">
+        <v>309</v>
+      </c>
       <c r="B313" s="15" t="s">
         <v>291</v>
       </c>
@@ -14098,7 +14274,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="6">
+        <v>310</v>
+      </c>
       <c r="B314" s="15" t="s">
         <v>291</v>
       </c>
@@ -14118,7 +14297,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="6">
+        <v>311</v>
+      </c>
       <c r="B315" s="15" t="s">
         <v>291</v>
       </c>
@@ -14138,7 +14320,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A316" s="6">
+        <v>312</v>
+      </c>
       <c r="B316" s="15" t="s">
         <v>291</v>
       </c>
@@ -14158,7 +14343,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A317" s="6">
+        <v>313</v>
+      </c>
       <c r="B317" s="15" t="s">
         <v>292</v>
       </c>
@@ -14178,7 +14366,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="6">
+        <v>314</v>
+      </c>
       <c r="B318" s="15" t="s">
         <v>292</v>
       </c>
@@ -14198,7 +14389,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A319" s="6">
+        <v>315</v>
+      </c>
       <c r="B319" s="15" t="s">
         <v>292</v>
       </c>
@@ -14218,7 +14412,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A320" s="6">
+        <v>316</v>
+      </c>
       <c r="B320" s="15" t="s">
         <v>292</v>
       </c>
@@ -14238,7 +14435,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="6">
+        <v>317</v>
+      </c>
       <c r="B321" s="15" t="s">
         <v>292</v>
       </c>
@@ -14258,7 +14458,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="6">
+        <v>318</v>
+      </c>
       <c r="B322" s="15" t="s">
         <v>292</v>
       </c>
@@ -14278,7 +14481,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="6">
+        <v>319</v>
+      </c>
       <c r="B323" s="16" t="s">
         <v>293</v>
       </c>
@@ -14298,7 +14504,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="6">
+        <v>320</v>
+      </c>
       <c r="B324" s="16" t="s">
         <v>294</v>
       </c>
@@ -14318,7 +14527,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A325" s="6">
+        <v>321</v>
+      </c>
       <c r="B325" s="16" t="s">
         <v>295</v>
       </c>
@@ -14338,7 +14550,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="326" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A326" s="6">
+        <v>322</v>
+      </c>
       <c r="B326" s="16" t="s">
         <v>296</v>
       </c>
@@ -14358,7 +14573,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="327" spans="2:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A327" s="6">
+        <v>323</v>
+      </c>
       <c r="B327" s="16" t="s">
         <v>297</v>
       </c>
@@ -14378,7 +14596,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="328" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A328" s="6">
+        <v>324</v>
+      </c>
       <c r="B328" s="17" t="s">
         <v>298</v>
       </c>
@@ -14398,7 +14619,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A329" s="6">
+        <v>325</v>
+      </c>
       <c r="B329" s="17" t="s">
         <v>299</v>
       </c>
@@ -14418,7 +14642,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="2:7" ht="231.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" ht="231.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A330" s="6">
+        <v>326</v>
+      </c>
       <c r="B330" s="17" t="s">
         <v>300</v>
       </c>
@@ -14438,7 +14665,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A331" s="6">
+        <v>327</v>
+      </c>
       <c r="B331" s="17" t="s">
         <v>301</v>
       </c>
@@ -14458,7 +14688,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="2:7" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A332" s="6">
+        <v>328</v>
+      </c>
       <c r="B332" s="17" t="s">
         <v>302</v>
       </c>
@@ -14478,7 +14711,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="2:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A333" s="6">
+        <v>329</v>
+      </c>
       <c r="B333" s="17" t="s">
         <v>303</v>
       </c>
@@ -14498,7 +14734,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A334" s="6">
+        <v>330</v>
+      </c>
       <c r="B334" s="17" t="s">
         <v>304</v>
       </c>
@@ -14518,7 +14757,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A335" s="6">
+        <v>331</v>
+      </c>
       <c r="B335" s="17" t="s">
         <v>305</v>
       </c>
@@ -14538,7 +14780,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="336" spans="2:7" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A336" s="6">
+        <v>332</v>
+      </c>
       <c r="B336" s="17" t="s">
         <v>306</v>
       </c>
@@ -14558,7 +14803,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A337" s="6">
+        <v>333</v>
+      </c>
       <c r="B337" s="17" t="s">
         <v>307</v>
       </c>
@@ -14578,7 +14826,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A338" s="6">
+        <v>334</v>
+      </c>
       <c r="B338" s="17" t="s">
         <v>308</v>
       </c>
@@ -14598,7 +14849,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="339" spans="2:7" ht="248.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" ht="248.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A339" s="6">
+        <v>335</v>
+      </c>
       <c r="B339" s="17" t="s">
         <v>309</v>
       </c>
@@ -14618,7 +14872,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A340" s="6">
+        <v>336</v>
+      </c>
       <c r="B340" s="17" t="s">
         <v>310</v>
       </c>
@@ -14638,7 +14895,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="341" spans="2:7" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A341" s="6">
+        <v>337</v>
+      </c>
       <c r="B341" s="17" t="s">
         <v>311</v>
       </c>
@@ -14658,7 +14918,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A342" s="6">
+        <v>338</v>
+      </c>
       <c r="B342" s="17" t="s">
         <v>312</v>
       </c>
@@ -14678,7 +14941,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A343" s="6">
+        <v>339</v>
+      </c>
       <c r="B343" s="17" t="s">
         <v>313</v>
       </c>
@@ -14698,7 +14964,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="2:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A344" s="6">
+        <v>340</v>
+      </c>
       <c r="B344" s="17" t="s">
         <v>314</v>
       </c>
@@ -14718,7 +14987,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A345" s="6">
+        <v>341</v>
+      </c>
       <c r="B345" s="17" t="s">
         <v>315</v>
       </c>
@@ -14738,7 +15010,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A346" s="6">
+        <v>342</v>
+      </c>
       <c r="B346" s="17" t="s">
         <v>316</v>
       </c>
@@ -14758,7 +15033,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A347" s="6">
+        <v>343</v>
+      </c>
       <c r="B347" s="17" t="s">
         <v>317</v>
       </c>
@@ -14778,7 +15056,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A348" s="6">
+        <v>344</v>
+      </c>
       <c r="B348" s="17" t="s">
         <v>318</v>
       </c>
@@ -14798,7 +15079,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A349" s="6">
+        <v>345</v>
+      </c>
       <c r="B349" s="17" t="s">
         <v>319</v>
       </c>
@@ -14818,7 +15102,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="2:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A350" s="6">
+        <v>346</v>
+      </c>
       <c r="B350" s="17" t="s">
         <v>320</v>
       </c>
@@ -14838,7 +15125,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A351" s="6">
+        <v>347</v>
+      </c>
       <c r="B351" s="17" t="s">
         <v>321</v>
       </c>
@@ -14858,7 +15148,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A352" s="6">
+        <v>348</v>
+      </c>
       <c r="B352" s="17" t="s">
         <v>322</v>
       </c>
@@ -14878,7 +15171,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A353" s="6">
+        <v>349</v>
+      </c>
       <c r="B353" s="17" t="s">
         <v>323</v>
       </c>
@@ -14898,7 +15194,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A354" s="6">
+        <v>350</v>
+      </c>
       <c r="B354" s="17" t="s">
         <v>324</v>
       </c>
@@ -14918,7 +15217,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A355" s="6">
+        <v>351</v>
+      </c>
       <c r="B355" s="17" t="s">
         <v>325</v>
       </c>
@@ -14938,7 +15240,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A356" s="6">
+        <v>352</v>
+      </c>
       <c r="B356" s="17" t="s">
         <v>326</v>
       </c>
@@ -14958,7 +15263,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A357" s="6">
+        <v>353</v>
+      </c>
       <c r="B357" s="17" t="s">
         <v>327</v>
       </c>
@@ -14978,7 +15286,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A358" s="6">
+        <v>354</v>
+      </c>
       <c r="B358" s="17" t="s">
         <v>328</v>
       </c>
@@ -14998,7 +15309,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A359" s="6">
+        <v>355</v>
+      </c>
       <c r="B359" s="17" t="s">
         <v>329</v>
       </c>
@@ -15018,7 +15332,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A360" s="6">
+        <v>356</v>
+      </c>
       <c r="B360" s="17" t="s">
         <v>330</v>
       </c>
@@ -15038,7 +15355,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A361" s="6">
+        <v>357</v>
+      </c>
       <c r="B361" s="17" t="s">
         <v>331</v>
       </c>
@@ -15058,7 +15378,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A362" s="6">
+        <v>358</v>
+      </c>
       <c r="B362" s="17" t="s">
         <v>332</v>
       </c>
@@ -15078,7 +15401,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A363" s="6">
+        <v>359</v>
+      </c>
       <c r="B363" s="17" t="s">
         <v>333</v>
       </c>
@@ -15098,7 +15424,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="2:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A364" s="6">
+        <v>360</v>
+      </c>
       <c r="B364" s="17" t="s">
         <v>334</v>
       </c>
@@ -15118,7 +15447,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A365" s="6">
+        <v>361</v>
+      </c>
       <c r="B365" s="17" t="s">
         <v>335</v>
       </c>
@@ -15138,7 +15470,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A366" s="6">
+        <v>362</v>
+      </c>
       <c r="B366" s="17" t="s">
         <v>336</v>
       </c>
@@ -15158,7 +15493,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="2:7" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A367" s="6">
+        <v>363</v>
+      </c>
       <c r="B367" s="17" t="s">
         <v>337</v>
       </c>
@@ -15178,7 +15516,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A368" s="6">
+        <v>364</v>
+      </c>
       <c r="B368" s="17" t="s">
         <v>338</v>
       </c>
@@ -15198,7 +15539,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A369" s="6">
+        <v>365</v>
+      </c>
       <c r="B369" s="17" t="s">
         <v>339</v>
       </c>
@@ -15218,7 +15562,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A370" s="6">
+        <v>366</v>
+      </c>
       <c r="B370" s="17" t="s">
         <v>340</v>
       </c>
@@ -15238,7 +15585,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A371" s="6">
+        <v>367</v>
+      </c>
       <c r="B371" s="17" t="s">
         <v>341</v>
       </c>
@@ -15258,7 +15608,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A372" s="6">
+        <v>368</v>
+      </c>
       <c r="B372" s="17" t="s">
         <v>342</v>
       </c>
@@ -15278,7 +15631,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="2:7" ht="198.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" ht="198.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A373" s="6">
+        <v>369</v>
+      </c>
       <c r="B373" s="17" t="s">
         <v>343</v>
       </c>
@@ -15298,7 +15654,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A374" s="6">
+        <v>370</v>
+      </c>
       <c r="B374" s="17" t="s">
         <v>343</v>
       </c>
@@ -15318,7 +15677,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A375" s="6">
+        <v>371</v>
+      </c>
       <c r="B375" s="18" t="s">
         <v>344</v>
       </c>
@@ -15338,7 +15700,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A376" s="6">
+        <v>372</v>
+      </c>
       <c r="B376" s="18" t="s">
         <v>345</v>
       </c>
@@ -15358,7 +15723,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="6">
+        <v>373</v>
+      </c>
       <c r="B377" s="18" t="s">
         <v>346</v>
       </c>
@@ -15378,7 +15746,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="6">
+        <v>374</v>
+      </c>
       <c r="B378" s="18" t="s">
         <v>347</v>
       </c>
@@ -15398,7 +15769,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A379" s="6">
+        <v>375</v>
+      </c>
       <c r="B379" s="18" t="s">
         <v>348</v>
       </c>
@@ -15418,7 +15792,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="6">
+        <v>376</v>
+      </c>
       <c r="B380" s="18" t="s">
         <v>349</v>
       </c>
@@ -15438,7 +15815,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A381" s="6">
+        <v>377</v>
+      </c>
       <c r="B381" s="18" t="s">
         <v>350</v>
       </c>
@@ -15458,7 +15838,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="6">
+        <v>378</v>
+      </c>
       <c r="B382" s="18" t="s">
         <v>351</v>
       </c>
@@ -15478,7 +15861,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="6">
+        <v>379</v>
+      </c>
       <c r="B383" s="18" t="s">
         <v>352</v>
       </c>
@@ -15498,7 +15884,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="6">
+        <v>380</v>
+      </c>
       <c r="B384" s="18" t="s">
         <v>353</v>
       </c>
@@ -15518,7 +15907,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="6">
+        <v>381</v>
+      </c>
       <c r="B385" s="18" t="s">
         <v>354</v>
       </c>
@@ -15538,7 +15930,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="6">
+        <v>382</v>
+      </c>
       <c r="B386" s="18" t="s">
         <v>355</v>
       </c>
@@ -15558,7 +15953,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="6">
+        <v>383</v>
+      </c>
       <c r="B387" s="19" t="s">
         <v>356</v>
       </c>
@@ -15578,7 +15976,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="6">
+        <v>384</v>
+      </c>
       <c r="B388" s="18" t="s">
         <v>357</v>
       </c>
@@ -15598,7 +15999,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="6">
+        <v>385</v>
+      </c>
       <c r="B389" s="18" t="s">
         <v>358</v>
       </c>
@@ -15618,7 +16022,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="6">
+        <v>386</v>
+      </c>
       <c r="B390" s="18" t="s">
         <v>359</v>
       </c>
@@ -15638,7 +16045,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="6">
+        <v>387</v>
+      </c>
       <c r="B391" s="18" t="s">
         <v>360</v>
       </c>
@@ -15658,7 +16068,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="392" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="6">
+        <v>388</v>
+      </c>
       <c r="B392" s="19" t="s">
         <v>361</v>
       </c>
@@ -15678,7 +16091,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="6">
+        <v>389</v>
+      </c>
       <c r="B393" s="19" t="s">
         <v>362</v>
       </c>
@@ -15698,7 +16114,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="6">
+        <v>390</v>
+      </c>
       <c r="B394" s="18" t="s">
         <v>363</v>
       </c>
@@ -15718,7 +16137,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="6">
+        <v>391</v>
+      </c>
       <c r="B395" s="18" t="s">
         <v>364</v>
       </c>
@@ -15738,7 +16160,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="6">
+        <v>392</v>
+      </c>
       <c r="B396" s="18" t="s">
         <v>365</v>
       </c>
@@ -15758,7 +16183,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="6">
+        <v>393</v>
+      </c>
       <c r="B397" s="19" t="s">
         <v>366</v>
       </c>
@@ -15778,7 +16206,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="6">
+        <v>394</v>
+      </c>
       <c r="B398" s="19" t="s">
         <v>367</v>
       </c>
@@ -15798,7 +16229,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="6">
+        <v>395</v>
+      </c>
       <c r="B399" s="18" t="s">
         <v>368</v>
       </c>
@@ -15818,7 +16252,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="6">
+        <v>396</v>
+      </c>
       <c r="B400" s="18" t="s">
         <v>369</v>
       </c>
@@ -15838,7 +16275,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="6">
+        <v>397</v>
+      </c>
       <c r="B401" s="19" t="s">
         <v>370</v>
       </c>
@@ -15858,7 +16298,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="402" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="6">
+        <v>398</v>
+      </c>
       <c r="B402" s="19" t="s">
         <v>371</v>
       </c>
@@ -15878,7 +16321,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="6">
+        <v>399</v>
+      </c>
       <c r="B403" s="20" t="s">
         <v>372</v>
       </c>
@@ -15898,7 +16344,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="6">
+        <v>400</v>
+      </c>
       <c r="B404" s="20" t="s">
         <v>373</v>
       </c>
@@ -15918,7 +16367,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="6">
+        <v>401</v>
+      </c>
       <c r="B405" s="20" t="s">
         <v>374</v>
       </c>
@@ -15938,7 +16390,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="2:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="6">
+        <v>402</v>
+      </c>
       <c r="B406" s="20" t="s">
         <v>375</v>
       </c>
@@ -15958,7 +16413,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="2:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="6">
+        <v>403</v>
+      </c>
       <c r="B407" s="20" t="s">
         <v>376</v>
       </c>
@@ -15978,7 +16436,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="408" spans="2:7" ht="68.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" ht="68.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A408" s="6">
+        <v>404</v>
+      </c>
       <c r="B408" s="20" t="s">
         <v>377</v>
       </c>
@@ -15998,7 +16459,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="409" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="6">
+        <v>405</v>
+      </c>
       <c r="B409" s="20" t="s">
         <v>378</v>
       </c>
@@ -16018,7 +16482,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="6">
+        <v>406</v>
+      </c>
       <c r="B410" s="20" t="s">
         <v>379</v>
       </c>
@@ -16038,7 +16505,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="411" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A411" s="6">
+        <v>407</v>
+      </c>
       <c r="B411" s="20" t="s">
         <v>380</v>
       </c>
@@ -16058,7 +16528,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="412" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A412" s="6">
+        <v>408</v>
+      </c>
       <c r="B412" s="20" t="s">
         <v>2</v>
       </c>
@@ -16078,7 +16551,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A413" s="6">
+        <v>409</v>
+      </c>
       <c r="B413" s="20" t="s">
         <v>381</v>
       </c>
@@ -16098,7 +16574,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="6">
+        <v>410</v>
+      </c>
       <c r="B414" s="20" t="s">
         <v>382</v>
       </c>
@@ -16118,7 +16597,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="415" spans="2:7" ht="68.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" ht="68.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="6">
+        <v>411</v>
+      </c>
       <c r="B415" s="20" t="s">
         <v>383</v>
       </c>
@@ -16138,7 +16620,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A416" s="6">
+        <v>412</v>
+      </c>
       <c r="B416" s="20" t="s">
         <v>384</v>
       </c>
@@ -16158,7 +16643,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="417" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="6">
+        <v>413</v>
+      </c>
       <c r="B417" s="21" t="s">
         <v>385</v>
       </c>
@@ -16178,7 +16666,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="6">
+        <v>414</v>
+      </c>
       <c r="B418" s="21" t="s">
         <v>386</v>
       </c>
@@ -16198,7 +16689,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="6">
+        <v>415</v>
+      </c>
       <c r="B419" s="21" t="s">
         <v>387</v>
       </c>
@@ -16218,7 +16712,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A420" s="6">
+        <v>416</v>
+      </c>
       <c r="B420" s="16" t="s">
         <v>388</v>
       </c>
@@ -16238,7 +16735,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A421" s="6">
+        <v>417</v>
+      </c>
       <c r="B421" s="21" t="s">
         <v>389</v>
       </c>
@@ -16258,7 +16758,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="422" spans="2:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="6">
+        <v>418</v>
+      </c>
       <c r="B422" s="21" t="s">
         <v>390</v>
       </c>
@@ -16278,7 +16781,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A423" s="6">
+        <v>419</v>
+      </c>
       <c r="B423" s="21" t="s">
         <v>391</v>
       </c>
@@ -16298,7 +16804,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="2:7" ht="215.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" ht="215.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A424" s="6">
+        <v>420</v>
+      </c>
       <c r="B424" s="21" t="s">
         <v>392</v>
       </c>
@@ -16318,7 +16827,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A425" s="6">
+        <v>421</v>
+      </c>
       <c r="B425" s="21" t="s">
         <v>393</v>
       </c>
@@ -16338,7 +16850,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A426" s="6">
+        <v>422</v>
+      </c>
       <c r="B426" s="21" t="s">
         <v>394</v>
       </c>
@@ -16358,7 +16873,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A427" s="6">
+        <v>423</v>
+      </c>
       <c r="B427" s="21" t="s">
         <v>395</v>
       </c>
@@ -16378,7 +16896,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A428" s="6">
+        <v>424</v>
+      </c>
       <c r="B428" s="21" t="s">
         <v>396</v>
       </c>
@@ -16398,7 +16919,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A429" s="6">
+        <v>425</v>
+      </c>
       <c r="B429" s="21" t="s">
         <v>397</v>
       </c>
@@ -16418,7 +16942,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A430" s="6">
+        <v>426</v>
+      </c>
       <c r="B430" s="21" t="s">
         <v>398</v>
       </c>
@@ -16438,7 +16965,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="2:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A431" s="6">
+        <v>427</v>
+      </c>
       <c r="B431" s="21" t="s">
         <v>399</v>
       </c>
@@ -16458,7 +16988,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A432" s="6">
+        <v>428</v>
+      </c>
       <c r="B432" s="21" t="s">
         <v>400</v>
       </c>
@@ -16478,7 +17011,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A433" s="6">
+        <v>429</v>
+      </c>
       <c r="B433" s="16" t="s">
         <v>401</v>
       </c>
@@ -16498,7 +17034,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="434" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A434" s="6">
+        <v>430</v>
+      </c>
       <c r="B434" s="21" t="s">
         <v>402</v>
       </c>
@@ -16518,7 +17057,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A435" s="6">
+        <v>431</v>
+      </c>
       <c r="B435" s="21" t="s">
         <v>403</v>
       </c>
@@ -16538,7 +17080,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A436" s="6">
+        <v>432</v>
+      </c>
       <c r="B436" s="21" t="s">
         <v>404</v>
       </c>
@@ -16558,7 +17103,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A437" s="6">
+        <v>433</v>
+      </c>
       <c r="B437" s="21" t="s">
         <v>405</v>
       </c>
@@ -16578,7 +17126,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A438" s="6">
+        <v>434</v>
+      </c>
       <c r="B438" s="21" t="s">
         <v>406</v>
       </c>
@@ -16598,7 +17149,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A439" s="6">
+        <v>435</v>
+      </c>
       <c r="B439" s="21" t="s">
         <v>407</v>
       </c>
@@ -16618,7 +17172,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A440" s="6">
+        <v>436</v>
+      </c>
       <c r="B440" s="21" t="s">
         <v>408</v>
       </c>
@@ -16638,7 +17195,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="441" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A441" s="6">
+        <v>437</v>
+      </c>
       <c r="B441" s="21" t="s">
         <v>409</v>
       </c>
@@ -16658,7 +17218,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="442" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A442" s="6">
+        <v>438</v>
+      </c>
       <c r="B442" s="21" t="s">
         <v>410</v>
       </c>
@@ -16678,7 +17241,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A443" s="6">
+        <v>439</v>
+      </c>
       <c r="B443" s="16" t="s">
         <v>411</v>
       </c>
@@ -16698,7 +17264,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="444" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A444" s="6">
+        <v>440</v>
+      </c>
       <c r="B444" s="16" t="s">
         <v>412</v>
       </c>
@@ -16718,7 +17287,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A445" s="6">
+        <v>441</v>
+      </c>
       <c r="B445" s="16" t="s">
         <v>413</v>
       </c>
@@ -16738,7 +17310,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A446" s="6">
+        <v>442</v>
+      </c>
       <c r="B446" s="16" t="s">
         <v>414</v>
       </c>
@@ -16758,7 +17333,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A447" s="6">
+        <v>443</v>
+      </c>
       <c r="B447" s="16" t="s">
         <v>415</v>
       </c>
@@ -16778,7 +17356,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="448" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A448" s="6">
+        <v>444</v>
+      </c>
       <c r="B448" s="16" t="s">
         <v>416</v>
       </c>
@@ -16798,7 +17379,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A449" s="6">
+        <v>445</v>
+      </c>
       <c r="B449" s="16" t="s">
         <v>417</v>
       </c>
@@ -16818,7 +17402,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A450" s="6">
+        <v>446</v>
+      </c>
       <c r="B450" s="16" t="s">
         <v>418</v>
       </c>
@@ -16838,7 +17425,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A451" s="6">
+        <v>447</v>
+      </c>
       <c r="B451" s="21" t="s">
         <v>419</v>
       </c>
@@ -16858,7 +17448,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A452" s="6">
+        <v>448</v>
+      </c>
       <c r="B452" s="21" t="s">
         <v>420</v>
       </c>
@@ -16878,7 +17471,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A453" s="6">
+        <v>449</v>
+      </c>
       <c r="B453" s="21" t="s">
         <v>421</v>
       </c>
@@ -16898,7 +17494,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="454" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A454" s="6">
+        <v>450</v>
+      </c>
       <c r="B454" s="21" t="s">
         <v>422</v>
       </c>
@@ -16918,7 +17517,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="455" spans="2:7" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A455" s="6">
+        <v>451</v>
+      </c>
       <c r="B455" s="21" t="s">
         <v>423</v>
       </c>
@@ -16938,7 +17540,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="456" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A456" s="6">
+        <v>452</v>
+      </c>
       <c r="B456" s="13" t="s">
         <v>424</v>
       </c>
@@ -16958,7 +17563,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A457" s="6">
+        <v>453</v>
+      </c>
       <c r="B457" s="22" t="s">
         <v>425</v>
       </c>
@@ -16978,7 +17586,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="458" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A458" s="6">
+        <v>454</v>
+      </c>
       <c r="B458" s="22" t="s">
         <v>426</v>
       </c>
@@ -16998,7 +17609,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A459" s="6">
+        <v>455</v>
+      </c>
       <c r="B459" s="9" t="s">
         <v>427</v>
       </c>
@@ -17018,7 +17632,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A460" s="6">
+        <v>456</v>
+      </c>
       <c r="B460" s="9" t="s">
         <v>428</v>
       </c>
@@ -17038,7 +17655,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A461" s="6">
+        <v>457</v>
+      </c>
       <c r="B461" s="9" t="s">
         <v>429</v>
       </c>
@@ -17058,7 +17678,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="462" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A462" s="6">
+        <v>458</v>
+      </c>
       <c r="B462" s="9" t="s">
         <v>430</v>
       </c>
@@ -17078,7 +17701,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="463" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A463" s="6">
+        <v>459</v>
+      </c>
       <c r="B463" s="9" t="s">
         <v>431</v>
       </c>
@@ -17098,7 +17724,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A464" s="6">
+        <v>460</v>
+      </c>
       <c r="B464" s="9" t="s">
         <v>432</v>
       </c>
@@ -17118,7 +17747,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A465" s="6">
+        <v>461</v>
+      </c>
       <c r="B465" s="9" t="s">
         <v>433</v>
       </c>
@@ -17138,7 +17770,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A466" s="6">
+        <v>462</v>
+      </c>
       <c r="B466" s="9" t="s">
         <v>434</v>
       </c>
@@ -17158,7 +17793,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="467" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A467" s="6">
+        <v>463</v>
+      </c>
       <c r="B467" s="9" t="s">
         <v>435</v>
       </c>
@@ -17178,7 +17816,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="468" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A468" s="6">
+        <v>464</v>
+      </c>
       <c r="B468" s="9" t="s">
         <v>436</v>
       </c>
@@ -17198,7 +17839,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A469" s="6">
+        <v>465</v>
+      </c>
       <c r="B469" s="9" t="s">
         <v>437</v>
       </c>
@@ -17218,7 +17862,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="470" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A470" s="6">
+        <v>466</v>
+      </c>
       <c r="B470" s="9" t="s">
         <v>438</v>
       </c>
@@ -17238,7 +17885,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A471" s="6">
+        <v>467</v>
+      </c>
       <c r="B471" s="9" t="s">
         <v>439</v>
       </c>
@@ -17258,7 +17908,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A472" s="6">
+        <v>468</v>
+      </c>
       <c r="B472" s="9" t="s">
         <v>440</v>
       </c>
@@ -17278,7 +17931,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="473" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A473" s="6">
+        <v>469</v>
+      </c>
       <c r="B473" s="9" t="s">
         <v>441</v>
       </c>
@@ -17298,7 +17954,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="474" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A474" s="6">
+        <v>470</v>
+      </c>
       <c r="B474" s="9" t="s">
         <v>442</v>
       </c>
@@ -17318,7 +17977,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="475" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A475" s="6">
+        <v>471</v>
+      </c>
       <c r="B475" s="9" t="s">
         <v>443</v>
       </c>
@@ -17338,7 +18000,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A476" s="6">
+        <v>472</v>
+      </c>
       <c r="B476" s="9" t="s">
         <v>444</v>
       </c>
@@ -17358,7 +18023,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="477" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A477" s="6">
+        <v>473</v>
+      </c>
       <c r="B477" s="9" t="s">
         <v>445</v>
       </c>
@@ -17378,7 +18046,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="478" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A478" s="6">
+        <v>474</v>
+      </c>
       <c r="B478" s="9" t="s">
         <v>446</v>
       </c>
@@ -17398,7 +18069,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="479" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A479" s="6">
+        <v>475</v>
+      </c>
       <c r="B479" s="16" t="s">
         <v>447</v>
       </c>
@@ -17418,7 +18092,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A480" s="6">
+        <v>476</v>
+      </c>
       <c r="B480" s="9" t="s">
         <v>448</v>
       </c>
@@ -17438,7 +18115,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="481" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A481" s="6">
+        <v>477</v>
+      </c>
       <c r="B481" s="9" t="s">
         <v>449</v>
       </c>
@@ -17458,7 +18138,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A482" s="6">
+        <v>478</v>
+      </c>
       <c r="B482" s="9" t="s">
         <v>450</v>
       </c>
@@ -17478,7 +18161,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A483" s="6">
+        <v>479</v>
+      </c>
       <c r="B483" s="9" t="s">
         <v>451</v>
       </c>
@@ -17498,7 +18184,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A484" s="6">
+        <v>480</v>
+      </c>
       <c r="B484" s="9" t="s">
         <v>452</v>
       </c>
@@ -17518,7 +18207,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="485" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A485" s="6">
+        <v>481</v>
+      </c>
       <c r="B485" s="9" t="s">
         <v>453</v>
       </c>
@@ -17538,7 +18230,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="486" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A486" s="6">
+        <v>482</v>
+      </c>
       <c r="B486" s="9" t="s">
         <v>454</v>
       </c>
@@ -17558,7 +18253,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A487" s="6">
+        <v>483</v>
+      </c>
       <c r="B487" s="9" t="s">
         <v>455</v>
       </c>
@@ -17578,7 +18276,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A488" s="6">
+        <v>484</v>
+      </c>
       <c r="B488" s="9" t="s">
         <v>456</v>
       </c>
@@ -17598,7 +18299,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="489" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A489" s="6">
+        <v>485</v>
+      </c>
       <c r="B489" s="9" t="s">
         <v>457</v>
       </c>
@@ -17618,7 +18322,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A490" s="6">
+        <v>486</v>
+      </c>
       <c r="B490" s="9" t="s">
         <v>458</v>
       </c>
@@ -17638,7 +18345,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="491" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A491" s="6">
+        <v>487</v>
+      </c>
       <c r="B491" s="9" t="s">
         <v>459</v>
       </c>
@@ -17658,7 +18368,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A492" s="6">
+        <v>488</v>
+      </c>
       <c r="B492" s="9" t="s">
         <v>460</v>
       </c>
@@ -17678,7 +18391,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="493" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A493" s="6">
+        <v>489</v>
+      </c>
       <c r="B493" s="9" t="s">
         <v>461</v>
       </c>
@@ -17698,7 +18414,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="494" spans="2:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A494" s="6">
+        <v>490</v>
+      </c>
       <c r="B494" s="9" t="s">
         <v>462</v>
       </c>
@@ -17718,7 +18437,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A495" s="6">
+        <v>491</v>
+      </c>
       <c r="B495" s="9" t="s">
         <v>463</v>
       </c>
@@ -17738,7 +18460,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A496" s="6">
+        <v>492</v>
+      </c>
       <c r="B496" s="9" t="s">
         <v>464</v>
       </c>
@@ -17758,7 +18483,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="497" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A497" s="6">
+        <v>493</v>
+      </c>
       <c r="B497" s="9" t="s">
         <v>465</v>
       </c>
@@ -17778,7 +18506,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="498" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A498" s="6">
+        <v>494</v>
+      </c>
       <c r="B498" s="9" t="s">
         <v>466</v>
       </c>
@@ -17798,7 +18529,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="2:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A499" s="6">
+        <v>495</v>
+      </c>
       <c r="B499" s="9" t="s">
         <v>467</v>
       </c>
@@ -17818,7 +18552,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A500" s="6">
+        <v>496</v>
+      </c>
       <c r="B500" s="9" t="s">
         <v>468</v>
       </c>
@@ -17838,7 +18575,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="501" spans="2:7" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:7" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A501" s="6">
+        <v>497</v>
+      </c>
       <c r="B501" s="9" t="s">
         <v>469</v>
       </c>
@@ -17858,7 +18598,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A502" s="6">
+        <v>498</v>
+      </c>
       <c r="B502" s="9" t="s">
         <v>470</v>
       </c>
@@ -17878,7 +18621,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A503" s="6">
+        <v>499</v>
+      </c>
       <c r="B503" s="9" t="s">
         <v>471</v>
       </c>
@@ -17898,7 +18644,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="504" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A504" s="6">
+        <v>500</v>
+      </c>
       <c r="B504" s="9" t="s">
         <v>472</v>
       </c>
@@ -17918,7 +18667,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A505" s="6">
+        <v>501</v>
+      </c>
       <c r="B505" s="9" t="s">
         <v>473</v>
       </c>
@@ -17938,7 +18690,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A506" s="6">
+        <v>502</v>
+      </c>
       <c r="B506" s="9" t="s">
         <v>474</v>
       </c>
@@ -17958,7 +18713,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A507" s="6">
+        <v>503</v>
+      </c>
       <c r="B507" s="9" t="s">
         <v>475</v>
       </c>
@@ -17978,7 +18736,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="508" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A508" s="6">
+        <v>504</v>
+      </c>
       <c r="B508" s="9" t="s">
         <v>476</v>
       </c>
@@ -17998,7 +18759,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A509" s="6">
+        <v>505</v>
+      </c>
       <c r="B509" s="9" t="s">
         <v>477</v>
       </c>
@@ -18018,7 +18782,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A510" s="6">
+        <v>506</v>
+      </c>
       <c r="B510" s="9" t="s">
         <v>478</v>
       </c>
@@ -18038,7 +18805,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A511" s="6">
+        <v>507</v>
+      </c>
       <c r="B511" s="16" t="s">
         <v>479</v>
       </c>
@@ -18058,7 +18828,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A512" s="6">
+        <v>508</v>
+      </c>
       <c r="B512" s="9" t="s">
         <v>480</v>
       </c>
@@ -18078,7 +18851,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A513" s="6">
+        <v>509</v>
+      </c>
       <c r="B513" s="16" t="s">
         <v>481</v>
       </c>
@@ -18098,7 +18874,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="514" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A514" s="6">
+        <v>510</v>
+      </c>
       <c r="B514" s="9" t="s">
         <v>482</v>
       </c>
@@ -18118,7 +18897,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="515" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A515" s="6">
+        <v>511</v>
+      </c>
       <c r="B515" s="16" t="s">
         <v>483</v>
       </c>
@@ -18138,7 +18920,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A516" s="6">
+        <v>512</v>
+      </c>
       <c r="B516" s="9" t="s">
         <v>484</v>
       </c>
@@ -18158,7 +18943,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A517" s="6">
+        <v>513</v>
+      </c>
       <c r="B517" s="9" t="s">
         <v>485</v>
       </c>
@@ -18178,7 +18966,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="518" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A518" s="6">
+        <v>514</v>
+      </c>
       <c r="B518" s="9" t="s">
         <v>486</v>
       </c>
@@ -18198,7 +18989,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A519" s="6">
+        <v>515</v>
+      </c>
       <c r="B519" s="9" t="s">
         <v>487</v>
       </c>
@@ -18218,7 +19012,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="6">
+        <v>516</v>
+      </c>
       <c r="B520" s="9" t="s">
         <v>488</v>
       </c>
@@ -18238,7 +19035,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="521" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A521" s="6">
+        <v>517</v>
+      </c>
       <c r="B521" s="9" t="s">
         <v>489</v>
       </c>
@@ -18258,7 +19058,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="522" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="6">
+        <v>518</v>
+      </c>
       <c r="B522" s="9" t="s">
         <v>490</v>
       </c>
@@ -18278,7 +19081,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="523" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A523" s="6">
+        <v>519</v>
+      </c>
       <c r="B523" s="9" t="s">
         <v>491</v>
       </c>
@@ -18298,7 +19104,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A524" s="6">
+        <v>520</v>
+      </c>
       <c r="B524" s="9" t="s">
         <v>492</v>
       </c>
@@ -18318,7 +19127,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="525" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A525" s="6">
+        <v>521</v>
+      </c>
       <c r="B525" s="9" t="s">
         <v>493</v>
       </c>
@@ -18338,7 +19150,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="526" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="6">
+        <v>522</v>
+      </c>
       <c r="B526" s="9" t="s">
         <v>494</v>
       </c>
@@ -18358,7 +19173,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="6">
+        <v>523</v>
+      </c>
       <c r="B527" s="9" t="s">
         <v>495</v>
       </c>
@@ -18378,7 +19196,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="528" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A528" s="6">
+        <v>524</v>
+      </c>
       <c r="B528" s="9" t="s">
         <v>496</v>
       </c>
@@ -18398,7 +19219,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A529" s="6">
+        <v>525</v>
+      </c>
       <c r="B529" s="21" t="s">
         <v>497</v>
       </c>
@@ -18418,7 +19242,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="6">
+        <v>526</v>
+      </c>
       <c r="B530" s="21" t="s">
         <v>498</v>
       </c>
@@ -18438,7 +19265,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="6">
+        <v>527</v>
+      </c>
       <c r="B531" s="19" t="s">
         <v>499</v>
       </c>
@@ -18458,7 +19288,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="6">
+        <v>528</v>
+      </c>
       <c r="B532" s="21" t="s">
         <v>500</v>
       </c>
@@ -18478,7 +19311,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A533" s="6">
+        <v>529</v>
+      </c>
       <c r="B533" s="16" t="s">
         <v>501</v>
       </c>
@@ -18498,7 +19334,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="534" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A534" s="6">
+        <v>530</v>
+      </c>
       <c r="B534" s="21" t="s">
         <v>502</v>
       </c>
@@ -18518,7 +19357,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A535" s="6">
+        <v>531</v>
+      </c>
       <c r="B535" s="21" t="s">
         <v>503</v>
       </c>
@@ -18538,7 +19380,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A536" s="6">
+        <v>532</v>
+      </c>
       <c r="B536" s="21" t="s">
         <v>504</v>
       </c>
@@ -18558,7 +19403,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A537" s="6">
+        <v>533</v>
+      </c>
       <c r="B537" s="21" t="s">
         <v>505</v>
       </c>
@@ -18578,7 +19426,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="538" spans="2:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:7" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A538" s="6">
+        <v>534</v>
+      </c>
       <c r="B538" s="21" t="s">
         <v>506</v>
       </c>
@@ -18598,7 +19449,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="539" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A539" s="6">
+        <v>535</v>
+      </c>
       <c r="B539" s="21" t="s">
         <v>507</v>
       </c>
@@ -18618,7 +19472,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A540" s="6">
+        <v>536</v>
+      </c>
       <c r="B540" s="21" t="s">
         <v>508</v>
       </c>
@@ -18638,7 +19495,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A541" s="6">
+        <v>537</v>
+      </c>
       <c r="B541" s="21" t="s">
         <v>509</v>
       </c>
@@ -18658,7 +19518,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="2:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A542" s="6">
+        <v>538</v>
+      </c>
       <c r="B542" s="21" t="s">
         <v>510</v>
       </c>
@@ -18678,7 +19541,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A543" s="6">
+        <v>539</v>
+      </c>
       <c r="B543" s="21" t="s">
         <v>511</v>
       </c>
@@ -18698,7 +19564,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="544" spans="2:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:7" ht="132.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A544" s="6">
+        <v>540</v>
+      </c>
       <c r="B544" s="21" t="s">
         <v>512</v>
       </c>
@@ -18718,7 +19587,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="545" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A545" s="6">
+        <v>541</v>
+      </c>
       <c r="B545" s="21" t="s">
         <v>513</v>
       </c>
@@ -18738,7 +19610,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="546" spans="2:7" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:7" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A546" s="6">
+        <v>542</v>
+      </c>
       <c r="B546" s="21" t="s">
         <v>514</v>
       </c>
@@ -18758,7 +19633,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A547" s="6">
+        <v>543</v>
+      </c>
       <c r="B547" s="21" t="s">
         <v>515</v>
       </c>
@@ -18778,7 +19656,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="548" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A548" s="6">
+        <v>544</v>
+      </c>
       <c r="B548" s="23" t="s">
         <v>516</v>
       </c>
@@ -18798,7 +19679,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="2:7" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:7" ht="81.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A549" s="6">
+        <v>545</v>
+      </c>
       <c r="B549" s="24" t="s">
         <v>517</v>
       </c>
@@ -18818,7 +19702,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="550" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A550" s="6">
+        <v>546</v>
+      </c>
       <c r="B550" s="24" t="s">
         <v>518</v>
       </c>
@@ -18838,7 +19725,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="551" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A551" s="6">
+        <v>547</v>
+      </c>
       <c r="B551" s="24" t="s">
         <v>519</v>
       </c>
@@ -18858,7 +19748,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="552" spans="2:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A552" s="6">
+        <v>548</v>
+      </c>
       <c r="B552" s="24" t="s">
         <v>520</v>
       </c>
@@ -18878,7 +19771,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="553" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A553" s="6">
+        <v>549</v>
+      </c>
       <c r="B553" s="23" t="s">
         <v>521</v>
       </c>
@@ -18898,7 +19794,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A554" s="6">
+        <v>550</v>
+      </c>
       <c r="B554" s="24" t="s">
         <v>522</v>
       </c>
@@ -18918,7 +19817,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A555" s="6">
+        <v>551</v>
+      </c>
       <c r="B555" s="23" t="s">
         <v>523</v>
       </c>
@@ -18938,7 +19840,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A556" s="6">
+        <v>552</v>
+      </c>
       <c r="B556" s="23" t="s">
         <v>524</v>
       </c>
@@ -18958,7 +19863,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="557" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A557" s="6">
+        <v>553</v>
+      </c>
       <c r="B557" s="23" t="s">
         <v>525</v>
       </c>
@@ -18978,7 +19886,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A558" s="6">
+        <v>554</v>
+      </c>
       <c r="B558" s="23" t="s">
         <v>526</v>
       </c>
@@ -18998,7 +19909,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="559" spans="2:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A559" s="6">
+        <v>555</v>
+      </c>
       <c r="B559" s="24" t="s">
         <v>527</v>
       </c>
@@ -19018,7 +19932,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="560" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A560" s="6">
+        <v>556</v>
+      </c>
       <c r="B560" s="24" t="s">
         <v>528</v>
       </c>
@@ -19038,7 +19955,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="561" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A561" s="6">
+        <v>557</v>
+      </c>
       <c r="B561" s="23" t="s">
         <v>529</v>
       </c>
@@ -19058,7 +19978,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="562" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A562" s="6">
+        <v>558</v>
+      </c>
       <c r="B562" s="24" t="s">
         <v>530</v>
       </c>
@@ -19078,7 +20001,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="563" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A563" s="6">
+        <v>559</v>
+      </c>
       <c r="B563" s="24" t="s">
         <v>531</v>
       </c>
@@ -19098,7 +20024,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="564" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A564" s="6">
+        <v>560</v>
+      </c>
       <c r="B564" s="23" t="s">
         <v>532</v>
       </c>
@@ -19118,7 +20047,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A565" s="6">
+        <v>561</v>
+      </c>
       <c r="B565" s="23" t="s">
         <v>533</v>
       </c>
@@ -19138,7 +20070,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A566" s="6">
+        <v>562</v>
+      </c>
       <c r="B566" s="24" t="s">
         <v>534</v>
       </c>
@@ -19158,7 +20093,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="567" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A567" s="6">
+        <v>563</v>
+      </c>
       <c r="B567" s="24" t="s">
         <v>535</v>
       </c>
@@ -19178,7 +20116,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="568" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A568" s="6">
+        <v>564</v>
+      </c>
       <c r="B568" s="24" t="s">
         <v>536</v>
       </c>
@@ -19198,7 +20139,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A569" s="6">
+        <v>565</v>
+      </c>
       <c r="B569" s="24" t="s">
         <v>537</v>
       </c>
@@ -19218,7 +20162,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="570" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A570" s="6">
+        <v>566</v>
+      </c>
       <c r="B570" s="24" t="s">
         <v>538</v>
       </c>
@@ -19238,7 +20185,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="571" spans="2:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:7" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A571" s="6">
+        <v>567</v>
+      </c>
       <c r="B571" s="23" t="s">
         <v>539</v>
       </c>
@@ -19258,7 +20208,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A572" s="6">
+        <v>568</v>
+      </c>
       <c r="B572" s="24" t="s">
         <v>540</v>
       </c>
@@ -19278,7 +20231,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="2:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:7" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A573" s="6">
+        <v>569</v>
+      </c>
       <c r="B573" s="24" t="s">
         <v>541</v>
       </c>
@@ -19298,7 +20254,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="574" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A574" s="6">
+        <v>570</v>
+      </c>
       <c r="B574" s="23" t="s">
         <v>542</v>
       </c>
@@ -19318,7 +20277,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="575" spans="2:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:7" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A575" s="6">
+        <v>571</v>
+      </c>
       <c r="B575" s="23" t="s">
         <v>543</v>
       </c>
